--- a/feedback_surveys/010_european_union_institutions_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/010_european_union_institutions_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eu_bodies</t>
+          <t>eu_trust</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EU Bodies</t>
+          <t>Do you trust the European Union institutions?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eu_bodies_2</t>
+          <t>eu_reasons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Other EU institution</t>
+          <t>What are your reasons for trusting or not trusting the European Union?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eu_bodies_2</t>
+          <t>eu_trust_earned</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Please describe other EU institution</t>
+          <t>Which institution has earned your trust?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eu_bodies_3</t>
+          <t>other_comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Why do you think this institution has earned your trust?</t>
+          <t>Other comments about the European Union institutions?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eu_bodies_4</t>
+          <t>eu_improve</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Why do you think this institution has lost your trust?</t>
+          <t>How do you think the EU institutions could improve?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eu_bodies_5</t>
+          <t>eu_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How do you think the EU institutions could improve?</t>
+          <t>Other comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eu_bodies_6</t>
+          <t>eu_suggestions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other comments</t>
+          <t>Your suggestions</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eu_bodies_7</t>
+          <t>eu_improvement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other comments</t>
+          <t>Eu Improvement</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eu_bodies_8</t>
+          <t>eu_improvement_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other comments</t>
+          <t>Eu Improvement 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eu_bodies_9</t>
+          <t>eu_improvement_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other comments</t>
+          <t>Eu Improvement 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,315 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eu_bodies_10</t>
+          <t>eu_improvement_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other comments</t>
+          <t>Eu Improvement 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>eu_bodies_11</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>eu_bodies_12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>eu_bodies_13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>eu_bodies_14</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>eu_bodies_15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>eu_bodies_16</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>eu_bodies_17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>eu_bodies_18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>eu_bodies_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>eu_bodies_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>eu_bodies_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>eu_bodies_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>eu_bodies_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Other comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eu_bodies_choices</t>
+          <t>eu_trust_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eu_bodies_choices</t>
+          <t>eu_trust_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1165,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'european_parliament'}</t>
+          <t>european_parliament</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'European Parliament'}</t>
+          <t>European Parliament</t>
         </is>
       </c>
     </row>
@@ -1182,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'european_council'}</t>
+          <t>european_council</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'European Council'}</t>
+          <t>European Council</t>
         </is>
       </c>
     </row>
@@ -1199,29 +900,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'european_commission'}</t>
+          <t>european_commission</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'European Commission'}</t>
+          <t>European Commission</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>eu_bodies_choices</t>
+          <t>eu_trust_earned_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'european_central_bank'}</t>
+          <t>european_parliament</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'European Central Bank'}</t>
+          <t>European Parliament</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eu_trust_earned_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>european_council</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>European Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>eu_trust_earned_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>european_commission</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>European Commission</t>
         </is>
       </c>
     </row>
